--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102687</v>
+        <v>102714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484190</v>
+        <v>484186</v>
       </c>
       <c r="R2" t="n">
         <v>6588394</v>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102719</v>
+        <v>102721</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102721</v>
+        <v>102740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102740</v>
+        <v>102742</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102742</v>
+        <v>102743</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102743</v>
+        <v>102744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102744</v>
+        <v>102750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20565-2025 artfynd.xlsx
+++ b/artfynd/A 20565-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135661769</v>
       </c>
       <c r="B2" t="n">
-        <v>102750</v>
+        <v>102751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
